--- a/arquivos/provedores_nuvem.xlsx
+++ b/arquivos/provedores_nuvem.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F257064\Documents\Codes\BLC TERCEIROS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F257064\Documents\Codes\BLC TERCEIROS\arquivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63A7C86-54BD-4D75-93FC-B117BC2EAB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04EB0DED-D197-4745-B824-9AA9FE29486B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
     <t>GIGA+</t>
   </si>
   <si>
-    <t>AMERICA NET</t>
+    <t>VERO</t>
   </si>
 </sst>
 </file>

--- a/arquivos/provedores_nuvem.xlsx
+++ b/arquivos/provedores_nuvem.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F257064\Documents\Codes\BLC TERCEIROS\arquivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04EB0DED-D197-4745-B824-9AA9FE29486B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F89D34-EF3B-424E-A542-0C763893F784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>ID</t>
   </si>
@@ -64,6 +64,21 @@
   </si>
   <si>
     <t>VERO</t>
+  </si>
+  <si>
+    <t>ATIVA TELECOM-MG</t>
+  </si>
+  <si>
+    <t>BRFIBRA</t>
+  </si>
+  <si>
+    <t>BRSULNET</t>
+  </si>
+  <si>
+    <t>SEBRATEL</t>
+  </si>
+  <si>
+    <t>TELLIUS</t>
   </si>
 </sst>
 </file>
@@ -381,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.21875" bestFit="1" customWidth="1"/>
@@ -483,6 +498,46 @@
         <v>11</v>
       </c>
     </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
